--- a/AAII_Financials/Quarterly/BOTH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BOTH_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="92">
   <si>
     <t>BOTH</t>
   </si>
@@ -656,136 +656,140 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43373</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43190</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43008</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42916</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42825</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42735</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -873,8 +877,11 @@
       <c r="AE8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -962,8 +969,11 @@
       <c r="AE9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1051,8 +1061,11 @@
       <c r="AE10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1084,8 +1097,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1173,8 +1187,11 @@
       <c r="AE12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,8 +1279,11 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1351,8 +1371,11 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1440,8 +1463,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,8 +1496,9 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1559,8 +1586,11 @@
       <c r="AE17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1648,8 +1678,11 @@
       <c r="AE18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,8 +1714,9 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1770,8 +1804,11 @@
       <c r="AE20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1781,8 +1818,8 @@
       <c r="E21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F21" s="3">
-        <v>0</v>
+      <c r="F21" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G21" s="3">
         <v>0</v>
@@ -1853,14 +1890,17 @@
       <c r="AC21" s="3">
         <v>0</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>4</v>
+      <c r="AD21" s="3">
+        <v>0</v>
       </c>
       <c r="AE21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1948,8 +1988,11 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2037,8 +2080,11 @@
       <c r="AE23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2093,11 +2139,11 @@
       <c r="T24" s="3">
         <v>0</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V24" s="3">
-        <v>0</v>
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W24" s="3">
         <v>0</v>
@@ -2126,8 +2172,11 @@
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,8 +2264,11 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2304,8 +2356,11 @@
       <c r="AE26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2393,8 +2448,11 @@
       <c r="AE27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2540,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2517,8 +2578,8 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>4</v>
+      <c r="N29" s="3">
+        <v>0</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>4</v>
@@ -2529,11 +2590,11 @@
       <c r="Q29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>4</v>
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>4</v>
@@ -2541,11 +2602,11 @@
       <c r="U29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
-      <c r="W29" s="3" t="s">
-        <v>4</v>
+      <c r="V29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>4</v>
@@ -2553,11 +2614,11 @@
       <c r="Y29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>4</v>
+      <c r="Z29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>4</v>
@@ -2571,8 +2632,11 @@
       <c r="AE29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,8 +2816,11 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2838,8 +2908,11 @@
       <c r="AE32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2927,8 +3000,11 @@
       <c r="AE33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,8 +3092,11 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3105,102 +3184,108 @@
       <c r="AE35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43373</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43190</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43008</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42916</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42825</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42735</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,8 +3351,9 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3322,11 +3409,11 @@
         <v>0</v>
       </c>
       <c r="U41" s="3">
+        <v>0</v>
+      </c>
+      <c r="V41" s="3">
         <v>100</v>
       </c>
-      <c r="V41" s="3">
-        <v>0</v>
-      </c>
       <c r="W41" s="3">
         <v>0</v>
       </c>
@@ -3346,7 +3433,7 @@
         <v>0</v>
       </c>
       <c r="AC41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD41" s="3">
         <v>100</v>
@@ -3354,8 +3441,11 @@
       <c r="AE41" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3443,8 +3533,11 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3532,8 +3625,11 @@
       <c r="AE43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3621,8 +3717,11 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3704,14 +3803,17 @@
       <c r="AC45" s="3">
         <v>0</v>
       </c>
-      <c r="AD45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE45" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3767,11 +3869,11 @@
         <v>0</v>
       </c>
       <c r="U46" s="3">
+        <v>0</v>
+      </c>
+      <c r="V46" s="3">
         <v>100</v>
       </c>
-      <c r="V46" s="3">
-        <v>0</v>
-      </c>
       <c r="W46" s="3">
         <v>0</v>
       </c>
@@ -3791,7 +3893,7 @@
         <v>0</v>
       </c>
       <c r="AC46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD46" s="3">
         <v>100</v>
@@ -3799,8 +3901,11 @@
       <c r="AE46" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3888,28 +3993,31 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>4</v>
+      <c r="D48" s="3">
+        <v>0</v>
+      </c>
+      <c r="E48" s="3">
+        <v>0</v>
+      </c>
+      <c r="F48" s="3">
+        <v>0</v>
+      </c>
+      <c r="G48" s="3">
+        <v>0</v>
+      </c>
+      <c r="H48" s="3">
+        <v>0</v>
+      </c>
+      <c r="I48" s="3">
+        <v>0</v>
       </c>
       <c r="J48" s="3">
         <v>0</v>
@@ -3974,11 +4082,14 @@
       <c r="AD48" s="3">
         <v>0</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4066,8 +4177,11 @@
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,8 +4361,11 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4333,8 +4453,11 @@
       <c r="AE52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,8 +4545,11 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -4479,11 +4605,11 @@
         <v>0</v>
       </c>
       <c r="U54" s="3">
+        <v>0</v>
+      </c>
+      <c r="V54" s="3">
         <v>100</v>
       </c>
-      <c r="V54" s="3">
-        <v>0</v>
-      </c>
       <c r="W54" s="3">
         <v>0</v>
       </c>
@@ -4503,7 +4629,7 @@
         <v>0</v>
       </c>
       <c r="AC54" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD54" s="3">
         <v>100</v>
@@ -4511,8 +4637,11 @@
       <c r="AE54" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,8 +4707,9 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4616,16 +4747,16 @@
         <v>100</v>
       </c>
       <c r="O57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q57" s="3">
         <v>100</v>
       </c>
       <c r="R57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S57" s="3">
         <v>0</v>
@@ -4666,8 +4797,11 @@
       <c r="AE57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4708,7 +4842,7 @@
         <v>400</v>
       </c>
       <c r="P58" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="Q58" s="3">
         <v>300</v>
@@ -4729,7 +4863,7 @@
         <v>300</v>
       </c>
       <c r="W58" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="X58" s="3">
         <v>200</v>
@@ -4755,8 +4889,11 @@
       <c r="AE58" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4770,7 +4907,7 @@
         <v>200</v>
       </c>
       <c r="G59" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H59" s="3">
         <v>100</v>
@@ -4794,7 +4931,7 @@
         <v>100</v>
       </c>
       <c r="O59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P59" s="3">
         <v>0</v>
@@ -4844,13 +4981,16 @@
       <c r="AE59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="E60" s="3">
         <v>700</v>
@@ -4862,7 +5002,7 @@
         <v>700</v>
       </c>
       <c r="H60" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="I60" s="3">
         <v>600</v>
@@ -4874,7 +5014,7 @@
         <v>600</v>
       </c>
       <c r="L60" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="M60" s="3">
         <v>500</v>
@@ -4883,7 +5023,7 @@
         <v>500</v>
       </c>
       <c r="O60" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="P60" s="3">
         <v>400</v>
@@ -4895,22 +5035,22 @@
         <v>400</v>
       </c>
       <c r="S60" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="T60" s="3">
         <v>300</v>
       </c>
       <c r="U60" s="3">
+        <v>300</v>
+      </c>
+      <c r="V60" s="3">
         <v>400</v>
-      </c>
-      <c r="V60" s="3">
-        <v>300</v>
       </c>
       <c r="W60" s="3">
         <v>300</v>
       </c>
       <c r="X60" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Y60" s="3">
         <v>200</v>
@@ -4933,8 +5073,11 @@
       <c r="AE60" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5022,8 +5165,11 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5111,8 +5257,11 @@
       <c r="AE62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,13 +5533,16 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="E66" s="3">
         <v>700</v>
@@ -5396,7 +5554,7 @@
         <v>700</v>
       </c>
       <c r="H66" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="I66" s="3">
         <v>600</v>
@@ -5408,7 +5566,7 @@
         <v>600</v>
       </c>
       <c r="L66" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="M66" s="3">
         <v>500</v>
@@ -5417,7 +5575,7 @@
         <v>500</v>
       </c>
       <c r="O66" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="P66" s="3">
         <v>400</v>
@@ -5429,22 +5587,22 @@
         <v>400</v>
       </c>
       <c r="S66" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="T66" s="3">
         <v>300</v>
       </c>
       <c r="U66" s="3">
+        <v>300</v>
+      </c>
+      <c r="V66" s="3">
         <v>400</v>
-      </c>
-      <c r="V66" s="3">
-        <v>300</v>
       </c>
       <c r="W66" s="3">
         <v>300</v>
       </c>
       <c r="X66" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Y66" s="3">
         <v>200</v>
@@ -5467,8 +5625,11 @@
       <c r="AE66" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +5843,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5767,8 +5935,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,13 +6027,16 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-1200</v>
+        <v>-1300</v>
       </c>
       <c r="E72" s="3">
         <v>-1200</v>
@@ -5874,7 +6048,7 @@
         <v>-1200</v>
       </c>
       <c r="H72" s="3">
-        <v>-1100</v>
+        <v>-1200</v>
       </c>
       <c r="I72" s="3">
         <v>-1100</v>
@@ -5886,7 +6060,7 @@
         <v>-1100</v>
       </c>
       <c r="L72" s="3">
-        <v>-1000</v>
+        <v>-1100</v>
       </c>
       <c r="M72" s="3">
         <v>-1000</v>
@@ -5895,7 +6069,7 @@
         <v>-1000</v>
       </c>
       <c r="O72" s="3">
-        <v>-900</v>
+        <v>-1000</v>
       </c>
       <c r="P72" s="3">
         <v>-900</v>
@@ -5907,7 +6081,7 @@
         <v>-900</v>
       </c>
       <c r="S72" s="3">
-        <v>-800</v>
+        <v>-900</v>
       </c>
       <c r="T72" s="3">
         <v>-800</v>
@@ -5919,7 +6093,7 @@
         <v>-800</v>
       </c>
       <c r="W72" s="3">
-        <v>-700</v>
+        <v>-800</v>
       </c>
       <c r="X72" s="3">
         <v>-700</v>
@@ -5937,7 +6111,7 @@
         <v>-700</v>
       </c>
       <c r="AC72" s="3">
-        <v>-600</v>
+        <v>-700</v>
       </c>
       <c r="AD72" s="3">
         <v>-600</v>
@@ -5945,8 +6119,11 @@
       <c r="AE72" s="3">
         <v>-600</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3">
+        <v>-600</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,13 +6395,16 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>-700</v>
+        <v>-800</v>
       </c>
       <c r="E76" s="3">
         <v>-700</v>
@@ -6230,7 +6416,7 @@
         <v>-700</v>
       </c>
       <c r="H76" s="3">
-        <v>-600</v>
+        <v>-700</v>
       </c>
       <c r="I76" s="3">
         <v>-600</v>
@@ -6242,7 +6428,7 @@
         <v>-600</v>
       </c>
       <c r="L76" s="3">
-        <v>-500</v>
+        <v>-600</v>
       </c>
       <c r="M76" s="3">
         <v>-500</v>
@@ -6251,7 +6437,7 @@
         <v>-500</v>
       </c>
       <c r="O76" s="3">
-        <v>-400</v>
+        <v>-500</v>
       </c>
       <c r="P76" s="3">
         <v>-400</v>
@@ -6263,7 +6449,7 @@
         <v>-400</v>
       </c>
       <c r="S76" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="T76" s="3">
         <v>-300</v>
@@ -6278,7 +6464,7 @@
         <v>-300</v>
       </c>
       <c r="X76" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="Y76" s="3">
         <v>-200</v>
@@ -6293,7 +6479,7 @@
         <v>-200</v>
       </c>
       <c r="AC76" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AD76" s="3">
         <v>-100</v>
@@ -6301,8 +6487,11 @@
       <c r="AE76" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,102 +6579,108 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43373</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43190</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43008</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42916</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42825</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42735</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -6573,8 +6768,11 @@
       <c r="AE81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,8 +6804,9 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6617,8 +6816,8 @@
       <c r="E83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F83" s="3">
-        <v>0</v>
+      <c r="F83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G83" s="3">
         <v>0</v>
@@ -6689,14 +6888,17 @@
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>4</v>
+      <c r="AD83" s="3">
+        <v>0</v>
       </c>
       <c r="AE83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,8 +7354,11 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7229,8 +7446,11 @@
       <c r="AE89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,8 +7482,9 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7351,8 +7572,11 @@
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,8 +7756,11 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7616,10 +7846,13 @@
         <v>0</v>
       </c>
       <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +7884,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7740,8 +7974,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,8 +8250,11 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8064,13 +8310,13 @@
         <v>0</v>
       </c>
       <c r="U100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V100" s="3">
         <v>100</v>
       </c>
       <c r="W100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X100" s="3">
         <v>0</v>
@@ -8096,8 +8342,11 @@
       <c r="AE100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8185,8 +8434,11 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8272,6 +8524,9 @@
         <v>0</v>
       </c>
       <c r="AE102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BOTH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BOTH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="92">
   <si>
     <t>BOTH</t>
   </si>
@@ -656,140 +656,147 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -880,8 +887,14 @@
       <c r="AF8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -972,8 +985,14 @@
       <c r="AF9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1064,8 +1083,14 @@
       <c r="AF10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1098,8 +1123,10 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1190,8 +1217,14 @@
       <c r="AF12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,8 +1315,14 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1374,8 +1413,14 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1466,8 +1511,14 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,8 +1548,10 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1589,8 +1642,14 @@
       <c r="AF17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1681,8 +1740,14 @@
       <c r="AF18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,8 +1780,10 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1807,8 +1874,14 @@
       <c r="AF20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1818,14 +1891,14 @@
       <c r="E21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G21" s="3">
-        <v>0</v>
-      </c>
-      <c r="H21" s="3">
-        <v>0</v>
+      <c r="F21" s="3">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I21" s="3">
         <v>0</v>
@@ -1893,14 +1966,20 @@
       <c r="AD21" s="3">
         <v>0</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF21" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1991,8 +2070,14 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2083,8 +2168,14 @@
       <c r="AF23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2142,14 +2233,14 @@
       <c r="U24" s="3">
         <v>0</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>4</v>
+      <c r="V24" s="3">
+        <v>0</v>
       </c>
       <c r="W24" s="3">
         <v>0</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
+      <c r="X24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y24" s="3">
         <v>0</v>
@@ -2175,8 +2266,14 @@
       <c r="AF24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,8 +2364,14 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2359,8 +2462,14 @@
       <c r="AF26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2451,8 +2560,14 @@
       <c r="AF27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2658,14 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2581,11 +2702,11 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P29" s="3" t="s">
-        <v>4</v>
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
+        <v>0</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>4</v>
@@ -2593,38 +2714,38 @@
       <c r="R29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
+      <c r="S29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>4</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
+      <c r="W29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>4</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
+      <c r="AA29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>4</v>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>4</v>
@@ -2635,8 +2756,14 @@
       <c r="AF29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2854,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,8 +2952,14 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2911,8 +3050,14 @@
       <c r="AF32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3003,8 +3148,14 @@
       <c r="AF33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,8 +3246,14 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3187,105 +3344,117 @@
       <c r="AF35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3487,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,8 +3523,10 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3412,14 +3585,14 @@
         <v>0</v>
       </c>
       <c r="V41" s="3">
+        <v>0</v>
+      </c>
+      <c r="W41" s="3">
+        <v>0</v>
+      </c>
+      <c r="X41" s="3">
         <v>100</v>
       </c>
-      <c r="W41" s="3">
-        <v>0</v>
-      </c>
-      <c r="X41" s="3">
-        <v>0</v>
-      </c>
       <c r="Y41" s="3">
         <v>0</v>
       </c>
@@ -3436,16 +3609,22 @@
         <v>0</v>
       </c>
       <c r="AD41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF41" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH41" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3536,8 +3715,14 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3628,8 +3813,14 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3720,8 +3911,14 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3806,14 +4003,20 @@
       <c r="AD45" s="3">
         <v>0</v>
       </c>
-      <c r="AE45" s="3" t="s">
-        <v>4</v>
+      <c r="AE45" s="3">
+        <v>0</v>
       </c>
       <c r="AF45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3872,14 +4075,14 @@
         <v>0</v>
       </c>
       <c r="V46" s="3">
+        <v>0</v>
+      </c>
+      <c r="W46" s="3">
+        <v>0</v>
+      </c>
+      <c r="X46" s="3">
         <v>100</v>
       </c>
-      <c r="W46" s="3">
-        <v>0</v>
-      </c>
-      <c r="X46" s="3">
-        <v>0</v>
-      </c>
       <c r="Y46" s="3">
         <v>0</v>
       </c>
@@ -3896,16 +4099,22 @@
         <v>0</v>
       </c>
       <c r="AD46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF46" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH46" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3996,8 +4205,14 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4085,11 +4300,17 @@
       <c r="AE48" s="3">
         <v>0</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4180,8 +4401,14 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4499,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,8 +4597,14 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4456,8 +4695,14 @@
       <c r="AF52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,8 +4793,14 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -4608,14 +4859,14 @@
         <v>0</v>
       </c>
       <c r="V54" s="3">
+        <v>0</v>
+      </c>
+      <c r="W54" s="3">
+        <v>0</v>
+      </c>
+      <c r="X54" s="3">
         <v>100</v>
       </c>
-      <c r="W54" s="3">
-        <v>0</v>
-      </c>
-      <c r="X54" s="3">
-        <v>0</v>
-      </c>
       <c r="Y54" s="3">
         <v>0</v>
       </c>
@@ -4632,16 +4883,22 @@
         <v>0</v>
       </c>
       <c r="AD54" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE54" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF54" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH54" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4931,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,13 +4967,15 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E57" s="3">
         <v>100</v>
@@ -4750,19 +5011,19 @@
         <v>100</v>
       </c>
       <c r="P57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q57" s="3">
         <v>100</v>
       </c>
       <c r="R57" s="3">
+        <v>0</v>
+      </c>
+      <c r="S57" s="3">
         <v>100</v>
       </c>
-      <c r="S57" s="3">
-        <v>0</v>
-      </c>
       <c r="T57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U57" s="3">
         <v>0</v>
@@ -4800,8 +5061,14 @@
       <c r="AF57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4845,10 +5112,10 @@
         <v>400</v>
       </c>
       <c r="Q58" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="R58" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="S58" s="3">
         <v>300</v>
@@ -4866,10 +5133,10 @@
         <v>300</v>
       </c>
       <c r="X58" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Y58" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Z58" s="3">
         <v>200</v>
@@ -4892,8 +5159,14 @@
       <c r="AF58" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>200</v>
+      </c>
+      <c r="AH58" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4910,10 +5183,10 @@
         <v>200</v>
       </c>
       <c r="H59" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I59" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J59" s="3">
         <v>100</v>
@@ -4934,10 +5207,10 @@
         <v>100</v>
       </c>
       <c r="P59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R59" s="3">
         <v>0</v>
@@ -4984,8 +5257,14 @@
       <c r="AF59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4993,10 +5272,10 @@
         <v>800</v>
       </c>
       <c r="E60" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="F60" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="G60" s="3">
         <v>700</v>
@@ -5005,10 +5284,10 @@
         <v>700</v>
       </c>
       <c r="I60" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="J60" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="K60" s="3">
         <v>600</v>
@@ -5017,19 +5296,19 @@
         <v>600</v>
       </c>
       <c r="M60" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="N60" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="O60" s="3">
         <v>500</v>
       </c>
       <c r="P60" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="Q60" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="R60" s="3">
         <v>400</v>
@@ -5038,25 +5317,25 @@
         <v>400</v>
       </c>
       <c r="T60" s="3">
+        <v>400</v>
+      </c>
+      <c r="U60" s="3">
+        <v>400</v>
+      </c>
+      <c r="V60" s="3">
         <v>300</v>
-      </c>
-      <c r="U60" s="3">
-        <v>300</v>
-      </c>
-      <c r="V60" s="3">
-        <v>400</v>
       </c>
       <c r="W60" s="3">
         <v>300</v>
       </c>
       <c r="X60" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y60" s="3">
         <v>300</v>
       </c>
-      <c r="Y60" s="3">
-        <v>200</v>
-      </c>
       <c r="Z60" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AA60" s="3">
         <v>200</v>
@@ -5076,8 +5355,14 @@
       <c r="AF60" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3">
+        <v>200</v>
+      </c>
+      <c r="AH60" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5168,8 +5453,14 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5260,8 +5551,14 @@
       <c r="AF62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5649,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5747,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,8 +5845,14 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -5545,10 +5860,10 @@
         <v>800</v>
       </c>
       <c r="E66" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="F66" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="G66" s="3">
         <v>700</v>
@@ -5557,10 +5872,10 @@
         <v>700</v>
       </c>
       <c r="I66" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="J66" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="K66" s="3">
         <v>600</v>
@@ -5569,19 +5884,19 @@
         <v>600</v>
       </c>
       <c r="M66" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="N66" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="O66" s="3">
         <v>500</v>
       </c>
       <c r="P66" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="Q66" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="R66" s="3">
         <v>400</v>
@@ -5590,25 +5905,25 @@
         <v>400</v>
       </c>
       <c r="T66" s="3">
+        <v>400</v>
+      </c>
+      <c r="U66" s="3">
+        <v>400</v>
+      </c>
+      <c r="V66" s="3">
         <v>300</v>
-      </c>
-      <c r="U66" s="3">
-        <v>300</v>
-      </c>
-      <c r="V66" s="3">
-        <v>400</v>
       </c>
       <c r="W66" s="3">
         <v>300</v>
       </c>
       <c r="X66" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y66" s="3">
         <v>300</v>
       </c>
-      <c r="Y66" s="3">
-        <v>200</v>
-      </c>
       <c r="Z66" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AA66" s="3">
         <v>200</v>
@@ -5628,8 +5943,14 @@
       <c r="AF66" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3">
+        <v>200</v>
+      </c>
+      <c r="AH66" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5983,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +6077,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6175,14 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6273,14 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,8 +6371,14 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6039,10 +6386,10 @@
         <v>-1300</v>
       </c>
       <c r="E72" s="3">
-        <v>-1200</v>
+        <v>-1300</v>
       </c>
       <c r="F72" s="3">
-        <v>-1200</v>
+        <v>-1300</v>
       </c>
       <c r="G72" s="3">
         <v>-1200</v>
@@ -6051,10 +6398,10 @@
         <v>-1200</v>
       </c>
       <c r="I72" s="3">
-        <v>-1100</v>
+        <v>-1200</v>
       </c>
       <c r="J72" s="3">
-        <v>-1100</v>
+        <v>-1200</v>
       </c>
       <c r="K72" s="3">
         <v>-1100</v>
@@ -6063,19 +6410,19 @@
         <v>-1100</v>
       </c>
       <c r="M72" s="3">
-        <v>-1000</v>
+        <v>-1100</v>
       </c>
       <c r="N72" s="3">
-        <v>-1000</v>
+        <v>-1100</v>
       </c>
       <c r="O72" s="3">
         <v>-1000</v>
       </c>
       <c r="P72" s="3">
-        <v>-900</v>
+        <v>-1000</v>
       </c>
       <c r="Q72" s="3">
-        <v>-900</v>
+        <v>-1000</v>
       </c>
       <c r="R72" s="3">
         <v>-900</v>
@@ -6084,10 +6431,10 @@
         <v>-900</v>
       </c>
       <c r="T72" s="3">
-        <v>-800</v>
+        <v>-900</v>
       </c>
       <c r="U72" s="3">
-        <v>-800</v>
+        <v>-900</v>
       </c>
       <c r="V72" s="3">
         <v>-800</v>
@@ -6096,10 +6443,10 @@
         <v>-800</v>
       </c>
       <c r="X72" s="3">
-        <v>-700</v>
+        <v>-800</v>
       </c>
       <c r="Y72" s="3">
-        <v>-700</v>
+        <v>-800</v>
       </c>
       <c r="Z72" s="3">
         <v>-700</v>
@@ -6114,16 +6461,22 @@
         <v>-700</v>
       </c>
       <c r="AD72" s="3">
-        <v>-600</v>
+        <v>-700</v>
       </c>
       <c r="AE72" s="3">
-        <v>-600</v>
+        <v>-700</v>
       </c>
       <c r="AF72" s="3">
         <v>-600</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AH72" s="3">
+        <v>-600</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6567,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6665,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,8 +6763,14 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -6407,10 +6778,10 @@
         <v>-800</v>
       </c>
       <c r="E76" s="3">
-        <v>-700</v>
+        <v>-800</v>
       </c>
       <c r="F76" s="3">
-        <v>-700</v>
+        <v>-800</v>
       </c>
       <c r="G76" s="3">
         <v>-700</v>
@@ -6419,10 +6790,10 @@
         <v>-700</v>
       </c>
       <c r="I76" s="3">
-        <v>-600</v>
+        <v>-700</v>
       </c>
       <c r="J76" s="3">
-        <v>-600</v>
+        <v>-700</v>
       </c>
       <c r="K76" s="3">
         <v>-600</v>
@@ -6431,19 +6802,19 @@
         <v>-600</v>
       </c>
       <c r="M76" s="3">
-        <v>-500</v>
+        <v>-600</v>
       </c>
       <c r="N76" s="3">
-        <v>-500</v>
+        <v>-600</v>
       </c>
       <c r="O76" s="3">
         <v>-500</v>
       </c>
       <c r="P76" s="3">
-        <v>-400</v>
+        <v>-500</v>
       </c>
       <c r="Q76" s="3">
-        <v>-400</v>
+        <v>-500</v>
       </c>
       <c r="R76" s="3">
         <v>-400</v>
@@ -6452,10 +6823,10 @@
         <v>-400</v>
       </c>
       <c r="T76" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="U76" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="V76" s="3">
         <v>-300</v>
@@ -6467,10 +6838,10 @@
         <v>-300</v>
       </c>
       <c r="Y76" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="Z76" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="AA76" s="3">
         <v>-200</v>
@@ -6482,16 +6853,22 @@
         <v>-200</v>
       </c>
       <c r="AD76" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AE76" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AF76" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH76" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,105 +6959,117 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -6771,8 +7160,14 @@
       <c r="AF81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,19 +7200,21 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>4</v>
+      <c r="D83" s="3">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3">
+        <v>0</v>
       </c>
       <c r="G83" s="3">
         <v>0</v>
@@ -6891,14 +7288,20 @@
       <c r="AD83" s="3">
         <v>0</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF83" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7392,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7490,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7588,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7686,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,8 +7784,14 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7449,8 +7882,14 @@
       <c r="AF89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,8 +7922,10 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7575,8 +8016,14 @@
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +8114,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,8 +8212,14 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7849,10 +8308,16 @@
         <v>0</v>
       </c>
       <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8350,10 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7977,8 +8444,14 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8542,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8640,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,8 +8738,14 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8313,17 +8804,17 @@
         <v>0</v>
       </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>100</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
         <v>0</v>
       </c>
@@ -8345,8 +8836,14 @@
       <c r="AF100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8437,8 +8934,14 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8527,6 +9030,12 @@
         <v>0</v>
       </c>
       <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BOTH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BOTH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="92">
   <si>
     <t>BOTH</t>
   </si>
@@ -656,147 +656,151 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -893,8 +897,11 @@
       <c r="AH8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -991,8 +998,11 @@
       <c r="AH9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1089,8 +1099,11 @@
       <c r="AH10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1223,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,8 +1338,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1419,8 +1439,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1517,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,8 +1576,9 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1648,8 +1675,11 @@
       <c r="AH17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1746,8 +1776,11 @@
       <c r="AH18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,8 +1815,9 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1880,28 +1914,31 @@
       <c r="AH20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F21" s="3">
-        <v>0</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>4</v>
+      <c r="E21" s="3">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I21" s="3">
-        <v>0</v>
+      <c r="I21" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J21" s="3">
         <v>0</v>
@@ -1972,14 +2009,17 @@
       <c r="AF21" s="3">
         <v>0</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>4</v>
+      <c r="AG21" s="3">
+        <v>0</v>
       </c>
       <c r="AH21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2076,8 +2116,11 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2174,8 +2217,11 @@
       <c r="AH23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2239,11 +2285,11 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>0</v>
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z24" s="3">
         <v>0</v>
@@ -2272,8 +2318,11 @@
       <c r="AH24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,8 +2419,11 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2468,8 +2520,11 @@
       <c r="AH26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2566,8 +2621,11 @@
       <c r="AH27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2708,8 +2769,8 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>4</v>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>4</v>
@@ -2720,11 +2781,11 @@
       <c r="T29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>4</v>
+      <c r="U29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>4</v>
@@ -2732,11 +2793,11 @@
       <c r="X29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>4</v>
+      <c r="Y29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>4</v>
@@ -2744,11 +2805,11 @@
       <c r="AB29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>4</v>
+      <c r="AC29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>4</v>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,8 +3025,11 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3056,8 +3126,11 @@
       <c r="AH32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3154,8 +3227,11 @@
       <c r="AH33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,8 +3328,11 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3350,111 +3429,117 @@
       <c r="AH35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,8 +3611,9 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3591,11 +3678,11 @@
         <v>0</v>
       </c>
       <c r="X41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="3">
         <v>100</v>
       </c>
-      <c r="Y41" s="3">
-        <v>0</v>
-      </c>
       <c r="Z41" s="3">
         <v>0</v>
       </c>
@@ -3615,7 +3702,7 @@
         <v>0</v>
       </c>
       <c r="AF41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG41" s="3">
         <v>100</v>
@@ -3623,8 +3710,11 @@
       <c r="AH41" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI41" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3721,8 +3811,11 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3819,8 +3912,11 @@
       <c r="AH43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3917,8 +4013,11 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4009,14 +4108,17 @@
       <c r="AF45" s="3">
         <v>0</v>
       </c>
-      <c r="AG45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH45" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4081,11 +4183,11 @@
         <v>0</v>
       </c>
       <c r="X46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y46" s="3">
         <v>100</v>
       </c>
-      <c r="Y46" s="3">
-        <v>0</v>
-      </c>
       <c r="Z46" s="3">
         <v>0</v>
       </c>
@@ -4105,7 +4207,7 @@
         <v>0</v>
       </c>
       <c r="AF46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG46" s="3">
         <v>100</v>
@@ -4113,8 +4215,11 @@
       <c r="AH46" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4211,8 +4316,11 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4306,11 +4414,14 @@
       <c r="AG48" s="3">
         <v>0</v>
       </c>
-      <c r="AH48" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4407,8 +4518,11 @@
       <c r="AH49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,8 +4720,11 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4701,8 +4821,11 @@
       <c r="AH52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,8 +4922,11 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -4865,11 +4991,11 @@
         <v>0</v>
       </c>
       <c r="X54" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y54" s="3">
         <v>100</v>
       </c>
-      <c r="Y54" s="3">
-        <v>0</v>
-      </c>
       <c r="Z54" s="3">
         <v>0</v>
       </c>
@@ -4889,7 +5015,7 @@
         <v>0</v>
       </c>
       <c r="AF54" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG54" s="3">
         <v>100</v>
@@ -4897,8 +5023,11 @@
       <c r="AH54" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI54" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,8 +5099,9 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4978,7 +5109,7 @@
         <v>200</v>
       </c>
       <c r="E57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F57" s="3">
         <v>100</v>
@@ -5017,16 +5148,16 @@
         <v>100</v>
       </c>
       <c r="R57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T57" s="3">
         <v>100</v>
       </c>
       <c r="U57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V57" s="3">
         <v>0</v>
@@ -5067,13 +5198,16 @@
       <c r="AH57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E58" s="3">
         <v>400</v>
@@ -5118,7 +5252,7 @@
         <v>400</v>
       </c>
       <c r="S58" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="T58" s="3">
         <v>300</v>
@@ -5139,7 +5273,7 @@
         <v>300</v>
       </c>
       <c r="Z58" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AA58" s="3">
         <v>200</v>
@@ -5165,8 +5299,11 @@
       <c r="AH58" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5189,7 +5326,7 @@
         <v>200</v>
       </c>
       <c r="J59" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K59" s="3">
         <v>100</v>
@@ -5213,7 +5350,7 @@
         <v>100</v>
       </c>
       <c r="R59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S59" s="3">
         <v>0</v>
@@ -5263,13 +5400,16 @@
       <c r="AH59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="E60" s="3">
         <v>800</v>
@@ -5278,7 +5418,7 @@
         <v>800</v>
       </c>
       <c r="G60" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="H60" s="3">
         <v>700</v>
@@ -5290,7 +5430,7 @@
         <v>700</v>
       </c>
       <c r="K60" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="L60" s="3">
         <v>600</v>
@@ -5302,7 +5442,7 @@
         <v>600</v>
       </c>
       <c r="O60" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="P60" s="3">
         <v>500</v>
@@ -5311,7 +5451,7 @@
         <v>500</v>
       </c>
       <c r="R60" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="S60" s="3">
         <v>400</v>
@@ -5323,22 +5463,22 @@
         <v>400</v>
       </c>
       <c r="V60" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="W60" s="3">
         <v>300</v>
       </c>
       <c r="X60" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y60" s="3">
         <v>400</v>
-      </c>
-      <c r="Y60" s="3">
-        <v>300</v>
       </c>
       <c r="Z60" s="3">
         <v>300</v>
       </c>
       <c r="AA60" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AB60" s="3">
         <v>200</v>
@@ -5361,8 +5501,11 @@
       <c r="AH60" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5459,8 +5602,11 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5557,8 +5703,11 @@
       <c r="AH62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,13 +6006,16 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="E66" s="3">
         <v>800</v>
@@ -5866,7 +6024,7 @@
         <v>800</v>
       </c>
       <c r="G66" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="H66" s="3">
         <v>700</v>
@@ -5878,7 +6036,7 @@
         <v>700</v>
       </c>
       <c r="K66" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="L66" s="3">
         <v>600</v>
@@ -5890,7 +6048,7 @@
         <v>600</v>
       </c>
       <c r="O66" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="P66" s="3">
         <v>500</v>
@@ -5899,7 +6057,7 @@
         <v>500</v>
       </c>
       <c r="R66" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="S66" s="3">
         <v>400</v>
@@ -5911,22 +6069,22 @@
         <v>400</v>
       </c>
       <c r="V66" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="W66" s="3">
         <v>300</v>
       </c>
       <c r="X66" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y66" s="3">
         <v>400</v>
-      </c>
-      <c r="Y66" s="3">
-        <v>300</v>
       </c>
       <c r="Z66" s="3">
         <v>300</v>
       </c>
       <c r="AA66" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AB66" s="3">
         <v>200</v>
@@ -5949,8 +6107,11 @@
       <c r="AH66" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI66" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,13 +6548,16 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-1300</v>
+        <v>-1400</v>
       </c>
       <c r="E72" s="3">
         <v>-1300</v>
@@ -6392,7 +6566,7 @@
         <v>-1300</v>
       </c>
       <c r="G72" s="3">
-        <v>-1200</v>
+        <v>-1300</v>
       </c>
       <c r="H72" s="3">
         <v>-1200</v>
@@ -6404,7 +6578,7 @@
         <v>-1200</v>
       </c>
       <c r="K72" s="3">
-        <v>-1100</v>
+        <v>-1200</v>
       </c>
       <c r="L72" s="3">
         <v>-1100</v>
@@ -6416,7 +6590,7 @@
         <v>-1100</v>
       </c>
       <c r="O72" s="3">
-        <v>-1000</v>
+        <v>-1100</v>
       </c>
       <c r="P72" s="3">
         <v>-1000</v>
@@ -6425,7 +6599,7 @@
         <v>-1000</v>
       </c>
       <c r="R72" s="3">
-        <v>-900</v>
+        <v>-1000</v>
       </c>
       <c r="S72" s="3">
         <v>-900</v>
@@ -6437,7 +6611,7 @@
         <v>-900</v>
       </c>
       <c r="V72" s="3">
-        <v>-800</v>
+        <v>-900</v>
       </c>
       <c r="W72" s="3">
         <v>-800</v>
@@ -6449,7 +6623,7 @@
         <v>-800</v>
       </c>
       <c r="Z72" s="3">
-        <v>-700</v>
+        <v>-800</v>
       </c>
       <c r="AA72" s="3">
         <v>-700</v>
@@ -6467,7 +6641,7 @@
         <v>-700</v>
       </c>
       <c r="AF72" s="3">
-        <v>-600</v>
+        <v>-700</v>
       </c>
       <c r="AG72" s="3">
         <v>-600</v>
@@ -6475,8 +6649,11 @@
       <c r="AH72" s="3">
         <v>-600</v>
       </c>
-    </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3">
+        <v>-600</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,13 +6952,16 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>-800</v>
+        <v>-900</v>
       </c>
       <c r="E76" s="3">
         <v>-800</v>
@@ -6784,7 +6970,7 @@
         <v>-800</v>
       </c>
       <c r="G76" s="3">
-        <v>-700</v>
+        <v>-800</v>
       </c>
       <c r="H76" s="3">
         <v>-700</v>
@@ -6796,7 +6982,7 @@
         <v>-700</v>
       </c>
       <c r="K76" s="3">
-        <v>-600</v>
+        <v>-700</v>
       </c>
       <c r="L76" s="3">
         <v>-600</v>
@@ -6808,7 +6994,7 @@
         <v>-600</v>
       </c>
       <c r="O76" s="3">
-        <v>-500</v>
+        <v>-600</v>
       </c>
       <c r="P76" s="3">
         <v>-500</v>
@@ -6817,7 +7003,7 @@
         <v>-500</v>
       </c>
       <c r="R76" s="3">
-        <v>-400</v>
+        <v>-500</v>
       </c>
       <c r="S76" s="3">
         <v>-400</v>
@@ -6829,7 +7015,7 @@
         <v>-400</v>
       </c>
       <c r="V76" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="W76" s="3">
         <v>-300</v>
@@ -6844,7 +7030,7 @@
         <v>-300</v>
       </c>
       <c r="AA76" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="AB76" s="3">
         <v>-200</v>
@@ -6859,7 +7045,7 @@
         <v>-200</v>
       </c>
       <c r="AF76" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AG76" s="3">
         <v>-100</v>
@@ -6867,8 +7053,11 @@
       <c r="AH76" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI76" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,111 +7154,117 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7166,8 +7361,11 @@
       <c r="AH81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,8 +7400,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7294,14 +7493,17 @@
       <c r="AF83" s="3">
         <v>0</v>
       </c>
-      <c r="AG83" s="3" t="s">
-        <v>4</v>
+      <c r="AG83" s="3">
+        <v>0</v>
       </c>
       <c r="AH83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,8 +8004,11 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7888,8 +8105,11 @@
       <c r="AH89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,8 +8144,9 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8022,8 +8243,11 @@
       <c r="AH91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,8 +8445,11 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8314,10 +8544,13 @@
         <v>0</v>
       </c>
       <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI94" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,8 +8987,11 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8810,13 +9056,13 @@
         <v>0</v>
       </c>
       <c r="X100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y100" s="3">
         <v>100</v>
       </c>
       <c r="Z100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA100" s="3">
         <v>0</v>
@@ -8842,8 +9088,11 @@
       <c r="AH100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8940,8 +9189,11 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9036,6 +9288,9 @@
         <v>0</v>
       </c>
       <c r="AH102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="3">
         <v>0</v>
       </c>
     </row>
